--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8114-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8114-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A04ABE3-EC8D-4116-850B-179F2039EF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC28C3D4-EEAD-4058-BA22-AD930CB8531E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F8CB4812-0158-46E9-BB0B-EAEA2C1C7571}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D088E357-874C-4A79-87CA-454C1B746BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="8114-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1403,20 +1403,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC69F18-471E-4149-BB04-AAC7D4C7C6F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFE3D8B-2339-4545-BB9B-A5C44C4B2D35}">
   <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" customWidth="1"/>
-    <col min="4" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="7.77734375" customWidth="1"/>
+    <col min="1" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1444,7 +1444,7 @@
       <c r="Q1" s="28"/>
       <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1474,7 +1474,7 @@
       <c r="Q2" s="30"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1570,7 +1570,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="37">
         <v>2024</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>2023</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="37">
         <v>2022</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="35">
         <v>2021</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>2020</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="35">
         <v>2019</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2018</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="35">
         <v>2017</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>2016</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="35">
         <v>2015</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2014</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="35">
         <v>2013</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>8.06</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="35">
         <v>2011</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2010</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="35">
         <v>2009</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>9.4600000000000009</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2008</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="35">
         <v>2007</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2006</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="35">
         <v>2005</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2004</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="35">
         <v>2003</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
         <v>25</v>
       </c>
